--- a/docs/Mapping_casi_uso/matrimoni/Matr_010.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_010.xlsx
@@ -905,7 +905,7 @@
     <t>evento.datiEventoMatrimonio.padreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,2,4,5)</t>
   </si>
   <si>
     <t>Padre Sposa</t>
@@ -914,7 +914,7 @@
     <t>evento.datiEventoMatrimonio.padreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,2,4,5)</t>
   </si>
   <si>
     <t>Madre Sposo</t>
@@ -923,7 +923,7 @@
     <t>evento.datiEventoMatrimonio.madreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Impedimento - Sposo</t>
@@ -950,7 +950,7 @@
     <t>evento.datiEventoMatrimonio.madreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Impedimento - Sposa</t>
@@ -971,13 +971,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Figlio</t>
@@ -1016,7 +1016,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Atto Nascita Figlio</t>
@@ -1034,13 +1034,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Assenso figlio</t>
@@ -1067,7 +1067,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Dati Riconoscimento - Generalità discendenti - Matrimoni</t>
@@ -1220,13 +1220,13 @@
     <t>attoNotarile</t>
   </si>
   <si>
-    <t>Assistenza minore Sposo</t>
+    <t>Assistenza Sposo</t>
   </si>
   <si>
     <t>tipoAssistenteSposo</t>
   </si>
   <si>
-    <t>Assistenza minore Sposa</t>
+    <t>Assistenza Sposa</t>
   </si>
   <si>
     <t>tipoAssistenteSposa</t>
@@ -1330,7 +1330,7 @@
     <col min="4" max="4" width="68.45703125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="32.48828125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="27.3203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="218.19921875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="119.40625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11481,10 +11481,10 @@
         <v>295</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D442" s="2" t="s">
         <v>296</v>
@@ -12125,10 +12125,10 @@
         <v>298</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C470" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D470" s="2" t="s">
         <v>299</v>
@@ -12769,10 +12769,10 @@
         <v>301</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D498" s="2" t="s">
         <v>302</v>
@@ -13597,10 +13597,10 @@
         <v>310</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D534" s="2" t="s">
         <v>311</v>
@@ -14425,10 +14425,10 @@
         <v>317</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C570" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D570" s="2" t="s">
         <v>318</v>
@@ -15069,10 +15069,10 @@
         <v>320</v>
       </c>
       <c r="B598" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D598" s="2" t="s">
         <v>318</v>
@@ -17530,10 +17530,10 @@
         <v>338</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C705" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D705" s="2" t="s">
         <v>339</v>
@@ -18174,10 +18174,10 @@
         <v>341</v>
       </c>
       <c r="B733" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C733" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D733" s="2" t="s">
         <v>339</v>
@@ -20164,7 +20164,7 @@
         <v>403</v>
       </c>
       <c r="F819" s="2" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="G819" s="2" t="s">
         <v>64</v>

--- a/docs/Mapping_casi_uso/matrimoni/Matr_010.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_010.xlsx
@@ -8931,7 +8931,7 @@
         <v>221</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D331" s="2" t="s">
         <v>258</v>
